--- a/outputs/408-5.xlsx
+++ b/outputs/408-5.xlsx
@@ -52,9 +52,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,20 +76,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -139,11 +125,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,64 +325,64 @@
   <dimension ref="A1:E134"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="54.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>-74.96</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="1" t="n">
+        <v>-74.9599999999942</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>31422220</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">SUMIFS(D2:D135,E2:E135,0)</f>
-        <v>-74.96</v>
+        <v>-74.9599999999942</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
